--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -675,51 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113011959</v>
+        <v>119283189</v>
       </c>
       <c r="B2" t="n">
-        <v>106616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231768</v>
+        <v>223597</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Halsfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium longicollum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Dahlst. ex Zahn) Johanss. &amp; Sam.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sven-Jakobs, 400 m SO om, Hjd</t>
+          <t>Sven-Jakobs, 400 m SV, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -729,7 +712,7 @@
         <v>6965093</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +736,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Belägg EJe-2023-086. Det. T. Tyler, LD, okt 2023. Endast ett tidigare fynd i Härjedalen, enligt Virtuella Herbariet; Hugo Dahlstedt 1905 i Storsjö.</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,77 +750,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grusig vägren</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Torbjörn Tyler</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erling Jirle</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erling Jirle, Ola Elleström, Johan Lorentzon</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119283189</v>
+        <v>113011959</v>
       </c>
       <c r="B3" t="n">
-        <v>97827</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>231768</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Halsfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hieracium longicollum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dahlst. ex Zahn) Johanss. &amp; Sam.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sven-Jakobs, 400 m SV, Hjd</t>
+          <t>Sven-Jakobs, 400 m SO om, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -852,7 +822,7 @@
         <v>6965093</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Belägg EJe-2023-086. Det. T. Tyler, LD, okt 2023. Endast ett tidigare fynd i Härjedalen, enligt Virtuella Herbariet; Hugo Dahlstedt 1905 i Storsjö.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,23 +865,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+          <t>Grusig vägren</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Erling Jirle, Ola Elleström, Johan Lorentzon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119283189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113011959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>